--- a/utiles/CajaNegra.xlsx
+++ b/utiles/CajaNegra.xlsx
@@ -5,16 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres\Desktop\DAW\EntornosDeDesarrollo\TercerTrimestre\UsuarioTestCase\Utiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres\Desktop\DAW\EntornosDeDesarrollo\TercerTrimestre\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0102FE85-9A68-4B59-8ADD-F7A0DB5A602A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222CBBDC-52B7-4D7C-9E2B-44506F8DD46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CE" sheetId="1" r:id="rId1"/>
-    <sheet name="Pairwise" sheetId="2" r:id="rId2"/>
+    <sheet name="CE" sheetId="2" r:id="rId1"/>
+    <sheet name="CE reducido" sheetId="1" r:id="rId2"/>
+    <sheet name="CE Pairwise" sheetId="5" r:id="rId3"/>
+    <sheet name="VL" sheetId="3" r:id="rId4"/>
+    <sheet name="VL Reducido" sheetId="6" r:id="rId5"/>
+    <sheet name="PairwiseVL" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="187">
   <si>
     <t>Entrada</t>
   </si>
@@ -58,12 +62,6 @@
     <t>tamaño String 4</t>
   </si>
   <si>
-    <t>tamaño String 2</t>
-  </si>
-  <si>
-    <t>tamañoString 6</t>
-  </si>
-  <si>
     <t>CE2</t>
   </si>
   <si>
@@ -151,27 +149,6 @@
     <t>CE18</t>
   </si>
   <si>
-    <t>longitud 4</t>
-  </si>
-  <si>
-    <t>longitud 7</t>
-  </si>
-  <si>
-    <t>longitud1</t>
-  </si>
-  <si>
-    <t>añadir un carácter no alfanumerico "_"</t>
-  </si>
-  <si>
-    <t>solo letras y numeros minuscula</t>
-  </si>
-  <si>
-    <t>solo letras y numeros mayuscula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no incluir numeros </t>
-  </si>
-  <si>
     <t>CE19</t>
   </si>
   <si>
@@ -199,9 +176,6 @@
     <t>CE27</t>
   </si>
   <si>
-    <t>Tomate</t>
-  </si>
-  <si>
     <t>Password1</t>
   </si>
   <si>
@@ -247,12 +221,6 @@
     <t xml:space="preserve">Usuario nulo </t>
   </si>
   <si>
-    <t xml:space="preserve">Usuario con longitud mayor de 15 caracteres </t>
-  </si>
-  <si>
-    <t>Usuario con longitud menor de 5 caracteres</t>
-  </si>
-  <si>
     <t xml:space="preserve">Contraseña nula </t>
   </si>
   <si>
@@ -272,13 +240,364 @@
   </si>
   <si>
     <t xml:space="preserve">Contraseña con longitud menor de 8 caracteres </t>
+  </si>
+  <si>
+    <t>clases de equivaencia valida</t>
+  </si>
+  <si>
+    <t>clases de equivalencia invalida</t>
+  </si>
+  <si>
+    <t>tamaño string 2</t>
+  </si>
+  <si>
+    <t>tamaño string  6</t>
+  </si>
+  <si>
+    <t>tamaño string 3</t>
+  </si>
+  <si>
+    <t>tamaño string 4</t>
+  </si>
+  <si>
+    <t>tamaño string 5</t>
+  </si>
+  <si>
+    <t>edad 18</t>
+  </si>
+  <si>
+    <t>edad 19</t>
+  </si>
+  <si>
+    <t>edad 17</t>
+  </si>
+  <si>
+    <t>edad</t>
+  </si>
+  <si>
+    <t>VL1</t>
+  </si>
+  <si>
+    <t>VL2</t>
+  </si>
+  <si>
+    <t>VL3</t>
+  </si>
+  <si>
+    <t>VL4</t>
+  </si>
+  <si>
+    <t>VL5</t>
+  </si>
+  <si>
+    <t>VL6</t>
+  </si>
+  <si>
+    <t>VL7</t>
+  </si>
+  <si>
+    <t>VL8</t>
+  </si>
+  <si>
+    <t>TC1</t>
+  </si>
+  <si>
+    <t>TC2</t>
+  </si>
+  <si>
+    <t>TC3</t>
+  </si>
+  <si>
+    <t>TC4</t>
+  </si>
+  <si>
+    <t>TC5</t>
+  </si>
+  <si>
+    <t>TC6</t>
+  </si>
+  <si>
+    <t>TC7</t>
+  </si>
+  <si>
+    <t>TC8</t>
+  </si>
+  <si>
+    <t>TC9</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>Entada</t>
+  </si>
+  <si>
+    <t>Joel</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>Ka</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>Usuario con longitud menor de 3 caracteres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usuario con longitud mayor de 5 caracteres </t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>case</t>
+  </si>
+  <si>
+    <t>casecase</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case </t>
+  </si>
+  <si>
+    <t>CASE</t>
+  </si>
+  <si>
+    <t>Case12</t>
+  </si>
+  <si>
+    <t>ID1</t>
+  </si>
+  <si>
+    <t>ID2</t>
+  </si>
+  <si>
+    <t>ID3</t>
+  </si>
+  <si>
+    <t>ID4</t>
+  </si>
+  <si>
+    <t>ID5</t>
+  </si>
+  <si>
+    <t>ID6</t>
+  </si>
+  <si>
+    <t>ID7</t>
+  </si>
+  <si>
+    <t>ID8</t>
+  </si>
+  <si>
+    <t>ID9</t>
+  </si>
+  <si>
+    <t>ID10</t>
+  </si>
+  <si>
+    <t>ID11</t>
+  </si>
+  <si>
+    <t>ID12</t>
+  </si>
+  <si>
+    <t>ID13</t>
+  </si>
+  <si>
+    <t>ID14</t>
+  </si>
+  <si>
+    <t>ID15</t>
+  </si>
+  <si>
+    <t>ID16</t>
+  </si>
+  <si>
+    <t>ID17</t>
+  </si>
+  <si>
+    <t>ID18</t>
+  </si>
+  <si>
+    <t>ID19</t>
+  </si>
+  <si>
+    <t>ID20</t>
+  </si>
+  <si>
+    <t>ID21</t>
+  </si>
+  <si>
+    <t>ID22</t>
+  </si>
+  <si>
+    <t>ID23</t>
+  </si>
+  <si>
+    <t>ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caseca </t>
+  </si>
+  <si>
+    <t>VL9</t>
+  </si>
+  <si>
+    <t>VL10</t>
+  </si>
+  <si>
+    <t>VL11</t>
+  </si>
+  <si>
+    <t>VL12</t>
+  </si>
+  <si>
+    <t>VL13</t>
+  </si>
+  <si>
+    <t>lenght 4</t>
+  </si>
+  <si>
+    <t>lenght 3</t>
+  </si>
+  <si>
+    <t>lenght 5</t>
+  </si>
+  <si>
+    <t>lenght 6</t>
+  </si>
+  <si>
+    <t>lenght 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca </t>
+  </si>
+  <si>
+    <t>Case13</t>
+  </si>
+  <si>
+    <t>Case14</t>
+  </si>
+  <si>
+    <t>Case15</t>
+  </si>
+  <si>
+    <t>Case16</t>
+  </si>
+  <si>
+    <t>Case17</t>
+  </si>
+  <si>
+    <t>Case18</t>
+  </si>
+  <si>
+    <t>Case19</t>
+  </si>
+  <si>
+    <t>Case20</t>
+  </si>
+  <si>
+    <t>Case21</t>
+  </si>
+  <si>
+    <t>Case22</t>
+  </si>
+  <si>
+    <t>Case23</t>
+  </si>
+  <si>
+    <t>Case24</t>
+  </si>
+  <si>
+    <t>Case25</t>
+  </si>
+  <si>
+    <t>Case26</t>
+  </si>
+  <si>
+    <t>Case27</t>
+  </si>
+  <si>
+    <t>Case28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cas </t>
+  </si>
+  <si>
+    <t>cases</t>
+  </si>
+  <si>
+    <t>caseca</t>
+  </si>
+  <si>
+    <t>cas</t>
+  </si>
+  <si>
+    <t>TC10</t>
+  </si>
+  <si>
+    <t>TC11</t>
+  </si>
+  <si>
+    <t>TC12</t>
+  </si>
+  <si>
+    <t>TC13</t>
+  </si>
+  <si>
+    <t>TC14</t>
+  </si>
+  <si>
+    <t>TC15</t>
+  </si>
+  <si>
+    <t>TC16</t>
+  </si>
+  <si>
+    <t>TC17</t>
+  </si>
+  <si>
+    <t>TC18</t>
+  </si>
+  <si>
+    <t>TC19</t>
+  </si>
+  <si>
+    <t>TC20</t>
+  </si>
+  <si>
+    <t>TC21</t>
+  </si>
+  <si>
+    <t>TC22</t>
+  </si>
+  <si>
+    <t>TC23</t>
+  </si>
+  <si>
+    <t>TC24</t>
+  </si>
+  <si>
+    <t>TC25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,8 +642,27 @@
       <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,6 +702,17 @@
         <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -394,7 +743,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -412,6 +761,40 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -694,310 +1077,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" customWidth="1"/>
-    <col min="4" max="4" width="32.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="15.6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C9" r:id="rId1" xr:uid="{CB724898-591E-49AF-B02D-FB67D17702F4}"/>
-    <hyperlink ref="D10" r:id="rId2" xr:uid="{2672E7E0-D654-4799-BB4E-3139558551BB}"/>
-    <hyperlink ref="D11" r:id="rId3" xr:uid="{FD826E30-9D83-43D0-B0ED-05888BB18BE2}"/>
-    <hyperlink ref="D12" r:id="rId4" xr:uid="{D0FF97AC-1677-42D7-A6D7-CCA53E2B7CDE}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AACD7976-4AAB-42E1-86EC-FC25E31AF597}">
   <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
@@ -1029,39 +1108,39 @@
       <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>57</v>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1069,9 +1148,9 @@
         <v>7</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="7">
+        <v>13</v>
+      </c>
+      <c r="C6" s="10">
         <v>19</v>
       </c>
       <c r="D6" s="7"/>
@@ -1079,21 +1158,21 @@
     <row r="7" spans="1:4">
       <c r="A7" s="8"/>
       <c r="B7" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1101,121 +1180,121 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>20</v>
       </c>
       <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="8"/>
       <c r="B17" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="8"/>
       <c r="B18" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="8"/>
       <c r="B19" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="8"/>
       <c r="B20" s="8" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1223,81 +1302,81 @@
         <v>5</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="8"/>
       <c r="B22" s="8" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="8"/>
       <c r="B23" s="8" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="8"/>
       <c r="B25" s="8" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="8"/>
       <c r="B26" s="8" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="8"/>
       <c r="B27" s="8" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="8"/>
       <c r="B28" s="8" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1307,4 +1386,1982 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="4" max="4" width="32.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C9" r:id="rId1" xr:uid="{CB724898-591E-49AF-B02D-FB67D17702F4}"/>
+    <hyperlink ref="D10" r:id="rId2" xr:uid="{2672E7E0-D654-4799-BB4E-3139558551BB}"/>
+    <hyperlink ref="D11" r:id="rId3" xr:uid="{FD826E30-9D83-43D0-B0ED-05888BB18BE2}"/>
+    <hyperlink ref="D12" r:id="rId4" xr:uid="{D0FF97AC-1677-42D7-A6D7-CCA53E2B7CDE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{701AA52A-02EF-44F4-845F-45433AE1B5E9}">
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="19.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="14">
+        <v>19</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="14">
+        <v>19</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="G4" s="14">
+        <v>19</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="14">
+        <v>19</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="3">
+        <v>15</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="14">
+        <v>19</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="14">
+        <v>19</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="14">
+        <v>19</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="14">
+        <v>19</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="14">
+        <v>19</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="14">
+        <v>19</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="14">
+        <v>19</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="14">
+        <v>19</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="14">
+        <v>19</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="14">
+        <v>19</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" s="14">
+        <v>19</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="14">
+        <v>19</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="14">
+        <v>19</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G21" s="14">
+        <v>19</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G22" s="14">
+        <v>19</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="14">
+        <v>19</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G24" s="14">
+        <v>19</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{97E8DD15-BAE5-4CEE-BA6E-1DC1E05FDBED}"/>
+    <hyperlink ref="H8" r:id="rId2" xr:uid="{1C8F6A5B-2629-43BA-892D-285309DFA466}"/>
+    <hyperlink ref="H9" r:id="rId3" xr:uid="{855DCB96-13BA-4699-B649-EDB753C81AAD}"/>
+    <hyperlink ref="H10" r:id="rId4" xr:uid="{86A9E1FD-6579-4333-8EC5-62E79BB866A2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{574A0A0B-60AF-4A31-AF1A-690D092D7D1C}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="24.44140625" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="13"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="20"/>
+      <c r="B3" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="13"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="20"/>
+      <c r="B4" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="13"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="20"/>
+      <c r="B5" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="20"/>
+      <c r="B6" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="20"/>
+      <c r="B8" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="20"/>
+      <c r="B9" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="20"/>
+      <c r="B11" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="20"/>
+      <c r="B12" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="16"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="20"/>
+      <c r="B13" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="20"/>
+      <c r="B14" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="C15" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A10:A14"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE196F2B-C02F-46F3-83A3-1C42B9AEE754}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="24.109375" customWidth="1"/>
+    <col min="4" max="4" width="25.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="13"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="20"/>
+      <c r="B3" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="13"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="20"/>
+      <c r="B4" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="13"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="20"/>
+      <c r="B5" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="20"/>
+      <c r="B6" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="13">
+        <v>18</v>
+      </c>
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="20"/>
+      <c r="B8" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="13">
+        <v>19</v>
+      </c>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="20"/>
+      <c r="B9" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="20"/>
+      <c r="B11" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="20"/>
+      <c r="B12" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="16"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="20"/>
+      <c r="B13" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="20"/>
+      <c r="B14" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{016124F7-D22A-4C68-BD54-06A682FF5475}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="22">
+        <v>19</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3" s="22">
+        <v>18</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="22">
+        <v>18</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="22">
+        <v>19</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="22">
+        <v>18</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="22">
+        <v>19</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="23">
+        <v>17</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="23">
+        <v>18</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="23">
+        <v>19</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="23">
+        <v>17</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="23">
+        <v>19</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="23">
+        <v>17</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="23">
+        <v>17</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" s="23">
+        <v>18</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="23">
+        <v>17</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="23">
+        <v>19</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="23">
+        <v>17</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="23">
+        <v>18</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" s="23">
+        <v>19</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="23">
+        <v>18</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" s="23">
+        <v>17</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" s="23">
+        <v>18</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="23">
+        <v>19</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="23">
+        <v>17</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="23">
+        <v>19</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>